--- a/artfynd/A 14504-2020 artfynd.xlsx
+++ b/artfynd/A 14504-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14504-2020 artfynd.xlsx
+++ b/artfynd/A 14504-2020 artfynd.xlsx
@@ -3677,10 +3677,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119788802</v>
+        <v>119788809</v>
       </c>
       <c r="B30" t="n">
-        <v>90067</v>
+        <v>91863</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3689,25 +3689,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>256703</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>808823</v>
+        <v>808756</v>
       </c>
       <c r="R30" t="n">
-        <v>7257295</v>
+        <v>7257294</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3783,10 +3783,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119788809</v>
+        <v>119788802</v>
       </c>
       <c r="B31" t="n">
-        <v>91863</v>
+        <v>90067</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3795,25 +3795,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5966</v>
+        <v>256703</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3823,10 +3823,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>808756</v>
+        <v>808823</v>
       </c>
       <c r="R31" t="n">
-        <v>7257294</v>
+        <v>7257295</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 14504-2020 artfynd.xlsx
+++ b/artfynd/A 14504-2020 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119709360</v>
+        <v>119709383</v>
       </c>
       <c r="B4" t="n">
-        <v>91832</v>
+        <v>86336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>3595</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Siljansspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius dalecarlicus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>808653</v>
+        <v>808628</v>
       </c>
       <c r="R4" t="n">
-        <v>7257079</v>
+        <v>7257172</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,6 +993,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1015,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119709383</v>
+        <v>119709354</v>
       </c>
       <c r="B5" t="n">
-        <v>86336</v>
+        <v>96868</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,25 +1028,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3595</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Siljansspindling</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius dalecarlicus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>808628</v>
+        <v>808673</v>
       </c>
       <c r="R5" t="n">
-        <v>7257172</v>
+        <v>7257024</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1100,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119709354</v>
+        <v>119709337</v>
       </c>
       <c r="B6" t="n">
-        <v>96868</v>
+        <v>90509</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,25 +1134,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>808673</v>
+        <v>808664</v>
       </c>
       <c r="R6" t="n">
-        <v>7257024</v>
+        <v>7257170</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119709337</v>
+        <v>119709360</v>
       </c>
       <c r="B7" t="n">
-        <v>90509</v>
+        <v>91832</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,21 +1244,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>808664</v>
+        <v>808653</v>
       </c>
       <c r="R7" t="n">
-        <v>7257170</v>
+        <v>7257079</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119709382</v>
+        <v>119709342</v>
       </c>
       <c r="B8" t="n">
-        <v>86381</v>
+        <v>90334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1346,25 +1346,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>248955</v>
+        <v>3215</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>808713</v>
+        <v>808681</v>
       </c>
       <c r="R8" t="n">
-        <v>7257204</v>
+        <v>7257040</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1418,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1441,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119709352</v>
+        <v>119709382</v>
       </c>
       <c r="B9" t="n">
-        <v>90097</v>
+        <v>86381</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,21 +1456,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5747</v>
+        <v>248955</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1481,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>808716</v>
+        <v>808713</v>
       </c>
       <c r="R9" t="n">
-        <v>7257151</v>
+        <v>7257204</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,6 +1524,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1547,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119709342</v>
+        <v>119709352</v>
       </c>
       <c r="B10" t="n">
-        <v>90334</v>
+        <v>90097</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,25 +1559,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3215</v>
+        <v>5747</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>808681</v>
+        <v>808716</v>
       </c>
       <c r="R10" t="n">
-        <v>7257040</v>
+        <v>7257151</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119745814</v>
+        <v>119745816</v>
       </c>
       <c r="B15" t="n">
-        <v>91861</v>
+        <v>91840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2094,37 +2094,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Degerberget, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>808701</v>
+        <v>808568</v>
       </c>
       <c r="R15" t="n">
-        <v>7257191</v>
+        <v>7256921</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,7 +2162,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2188,10 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119745816</v>
+        <v>119745817</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>95202</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2204,21 +2200,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>808568</v>
+        <v>808679</v>
       </c>
       <c r="R16" t="n">
-        <v>7256921</v>
+        <v>7257181</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2294,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119745817</v>
+        <v>119745814</v>
       </c>
       <c r="B17" t="n">
-        <v>95202</v>
+        <v>91861</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2310,34 +2306,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2869</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Degerberget, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>808679</v>
+        <v>808701</v>
       </c>
       <c r="R17" t="n">
-        <v>7257181</v>
+        <v>7257191</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2378,6 +2377,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2400,10 +2400,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119788811</v>
+        <v>119788793</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>87406</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,25 +2412,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>808704</v>
+        <v>808662</v>
       </c>
       <c r="R18" t="n">
-        <v>7257179</v>
+        <v>7257218</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2506,10 +2506,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119788831</v>
+        <v>119788791</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>87406</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2518,25 +2518,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>4412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>808801</v>
+        <v>808629</v>
       </c>
       <c r="R19" t="n">
-        <v>7257314</v>
+        <v>7257001</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2612,10 +2612,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119788819</v>
+        <v>119788805</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>91832</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2624,25 +2624,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>808646</v>
+        <v>808423</v>
       </c>
       <c r="R20" t="n">
-        <v>7257196</v>
+        <v>7257034</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119788805</v>
+        <v>119788803</v>
       </c>
       <c r="B22" t="n">
-        <v>91832</v>
+        <v>86336</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>3595</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Siljansspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius dalecarlicus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>808423</v>
+        <v>808624</v>
       </c>
       <c r="R22" t="n">
-        <v>7257034</v>
+        <v>7257193</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2908,6 +2908,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2930,10 +2931,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119788828</v>
+        <v>119788814</v>
       </c>
       <c r="B23" t="n">
-        <v>91861</v>
+        <v>97907</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,41 +2943,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Degerberget, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>808673</v>
+        <v>808920</v>
       </c>
       <c r="R23" t="n">
-        <v>7257226</v>
+        <v>7257293</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,7 +3015,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3040,10 +3037,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119788803</v>
+        <v>119788802</v>
       </c>
       <c r="B24" t="n">
-        <v>86336</v>
+        <v>90067</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3052,25 +3049,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3595</v>
+        <v>256703</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Siljansspindling</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius dalecarlicus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3080,10 +3077,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>808624</v>
+        <v>808823</v>
       </c>
       <c r="R24" t="n">
-        <v>7257193</v>
+        <v>7257295</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,7 +3121,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3147,10 +3143,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119788800</v>
+        <v>119788831</v>
       </c>
       <c r="B25" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3159,25 +3155,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3187,10 +3183,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>808485</v>
+        <v>808801</v>
       </c>
       <c r="R25" t="n">
-        <v>7256974</v>
+        <v>7257314</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3253,10 +3249,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119788791</v>
+        <v>119788812</v>
       </c>
       <c r="B26" t="n">
-        <v>87406</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3265,25 +3261,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3293,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>808629</v>
+        <v>808704</v>
       </c>
       <c r="R26" t="n">
-        <v>7257001</v>
+        <v>7257179</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3359,10 +3355,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119788793</v>
+        <v>119788800</v>
       </c>
       <c r="B27" t="n">
-        <v>87406</v>
+        <v>91463</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3375,21 +3371,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4412</v>
+        <v>4745</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3399,10 +3395,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>808662</v>
+        <v>808485</v>
       </c>
       <c r="R27" t="n">
-        <v>7257218</v>
+        <v>7256974</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3465,10 +3461,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119788807</v>
+        <v>119788804</v>
       </c>
       <c r="B28" t="n">
-        <v>94311</v>
+        <v>86453</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3477,25 +3473,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2809</v>
+        <v>3739</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3505,10 +3501,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>808927</v>
+        <v>808709</v>
       </c>
       <c r="R28" t="n">
-        <v>7257295</v>
+        <v>7257177</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3677,10 +3673,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119788809</v>
+        <v>119788813</v>
       </c>
       <c r="B30" t="n">
-        <v>91863</v>
+        <v>97907</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3689,25 +3685,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3717,10 +3713,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>808756</v>
+        <v>808757</v>
       </c>
       <c r="R30" t="n">
-        <v>7257294</v>
+        <v>7257182</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3783,10 +3779,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119788802</v>
+        <v>119788807</v>
       </c>
       <c r="B31" t="n">
-        <v>90067</v>
+        <v>94311</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3799,21 +3795,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>256703</v>
+        <v>2809</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3823,7 +3819,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>808823</v>
+        <v>808927</v>
       </c>
       <c r="R31" t="n">
         <v>7257295</v>
@@ -3889,7 +3885,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119788813</v>
+        <v>119788819</v>
       </c>
       <c r="B32" t="n">
         <v>97907</v>
@@ -3929,10 +3925,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>808757</v>
+        <v>808646</v>
       </c>
       <c r="R32" t="n">
-        <v>7257182</v>
+        <v>7257196</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3995,50 +3991,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119788804</v>
+        <v>119788827</v>
       </c>
       <c r="B33" t="n">
-        <v>86453</v>
+        <v>91861</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3739</v>
+        <v>5964</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Degerberget, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>808709</v>
+        <v>808723</v>
       </c>
       <c r="R33" t="n">
-        <v>7257177</v>
+        <v>7257161</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4079,6 +4078,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4101,37 +4101,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119788814</v>
+        <v>119788809</v>
       </c>
       <c r="B34" t="n">
-        <v>97907</v>
+        <v>91863</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>808920</v>
+        <v>808756</v>
       </c>
       <c r="R34" t="n">
-        <v>7257293</v>
+        <v>7257294</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4207,7 +4207,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119788827</v>
+        <v>119788828</v>
       </c>
       <c r="B35" t="n">
         <v>91861</v>
@@ -4250,10 +4250,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>808723</v>
+        <v>808673</v>
       </c>
       <c r="R35" t="n">
-        <v>7257161</v>
+        <v>7257226</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 14504-2020 artfynd.xlsx
+++ b/artfynd/A 14504-2020 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119709383</v>
+        <v>119709354</v>
       </c>
       <c r="B4" t="n">
-        <v>86336</v>
+        <v>96868</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3595</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Siljansspindling</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius dalecarlicus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>808628</v>
+        <v>808673</v>
       </c>
       <c r="R4" t="n">
-        <v>7257172</v>
+        <v>7257024</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1016,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119709354</v>
+        <v>119709337</v>
       </c>
       <c r="B5" t="n">
-        <v>96868</v>
+        <v>90509</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,25 +1027,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>808673</v>
+        <v>808664</v>
       </c>
       <c r="R5" t="n">
-        <v>7257024</v>
+        <v>7257170</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119709337</v>
+        <v>119709383</v>
       </c>
       <c r="B6" t="n">
-        <v>90509</v>
+        <v>86336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,25 +1133,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>3595</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Siljansspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Cortinarius dalecarlicus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>808664</v>
+        <v>808628</v>
       </c>
       <c r="R6" t="n">
-        <v>7257170</v>
+        <v>7257172</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,6 +1205,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14504-2020 artfynd.xlsx
+++ b/artfynd/A 14504-2020 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119709354</v>
+        <v>119709384</v>
       </c>
       <c r="B4" t="n">
-        <v>96868</v>
+        <v>86336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>3595</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Siljansspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cortinarius dalecarlicus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>808673</v>
+        <v>808638</v>
       </c>
       <c r="R4" t="n">
-        <v>7257024</v>
+        <v>7257171</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119709337</v>
+        <v>119709360</v>
       </c>
       <c r="B5" t="n">
-        <v>90509</v>
+        <v>91832</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>808664</v>
+        <v>808653</v>
       </c>
       <c r="R5" t="n">
-        <v>7257170</v>
+        <v>7257079</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1228,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119709360</v>
+        <v>119709337</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
+        <v>90509</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,21 +1244,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>808653</v>
+        <v>808664</v>
       </c>
       <c r="R7" t="n">
-        <v>7257079</v>
+        <v>7257170</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119709342</v>
+        <v>119709354</v>
       </c>
       <c r="B8" t="n">
-        <v>90334</v>
+        <v>96868</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3215</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>808681</v>
+        <v>808673</v>
       </c>
       <c r="R8" t="n">
-        <v>7257040</v>
+        <v>7257024</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1547,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119709352</v>
+        <v>119709342</v>
       </c>
       <c r="B10" t="n">
-        <v>90097</v>
+        <v>90334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,25 +1559,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5747</v>
+        <v>3215</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>808716</v>
+        <v>808681</v>
       </c>
       <c r="R10" t="n">
-        <v>7257151</v>
+        <v>7257040</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119709384</v>
+        <v>119709352</v>
       </c>
       <c r="B11" t="n">
-        <v>86336</v>
+        <v>90097</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3595</v>
+        <v>5747</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Siljansspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius dalecarlicus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>808638</v>
+        <v>808716</v>
       </c>
       <c r="R11" t="n">
-        <v>7257171</v>
+        <v>7257151</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119745790</v>
+        <v>119745816</v>
       </c>
       <c r="B12" t="n">
-        <v>87406</v>
+        <v>91840</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,25 +1771,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>808771</v>
+        <v>808568</v>
       </c>
       <c r="R12" t="n">
-        <v>7257171</v>
+        <v>7256921</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119745805</v>
+        <v>119745789</v>
       </c>
       <c r="B13" t="n">
-        <v>86336</v>
+        <v>87406</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,25 +1877,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3595</v>
+        <v>4412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Siljansspindling</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius dalecarlicus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>808703</v>
+        <v>808556</v>
       </c>
       <c r="R13" t="n">
-        <v>7257179</v>
+        <v>7256898</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,7 +1949,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1972,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119745789</v>
+        <v>119745814</v>
       </c>
       <c r="B14" t="n">
-        <v>87406</v>
+        <v>91861</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,38 +1983,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4412</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Degerberget, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>808556</v>
+        <v>808701</v>
       </c>
       <c r="R14" t="n">
-        <v>7256898</v>
+        <v>7257191</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,6 +2058,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2078,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119745816</v>
+        <v>119745805</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>86336</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,25 +2093,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>3595</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Siljansspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius dalecarlicus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2118,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>808568</v>
+        <v>808703</v>
       </c>
       <c r="R15" t="n">
-        <v>7256921</v>
+        <v>7257179</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,6 +2165,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2290,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119745814</v>
+        <v>119745790</v>
       </c>
       <c r="B17" t="n">
-        <v>91861</v>
+        <v>87406</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2302,41 +2306,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>4412</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Degerberget, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>808701</v>
+        <v>808771</v>
       </c>
       <c r="R17" t="n">
-        <v>7257191</v>
+        <v>7257171</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,7 +2378,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2400,10 +2400,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119788793</v>
+        <v>119788807</v>
       </c>
       <c r="B18" t="n">
-        <v>87406</v>
+        <v>94311</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,25 +2412,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4412</v>
+        <v>2809</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>808662</v>
+        <v>808927</v>
       </c>
       <c r="R18" t="n">
-        <v>7257218</v>
+        <v>7257295</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2506,10 +2506,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119788791</v>
+        <v>119788831</v>
       </c>
       <c r="B19" t="n">
-        <v>87406</v>
+        <v>91840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2518,25 +2518,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>808629</v>
+        <v>808801</v>
       </c>
       <c r="R19" t="n">
-        <v>7257001</v>
+        <v>7257314</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119788801</v>
+        <v>119788804</v>
       </c>
       <c r="B21" t="n">
-        <v>91463</v>
+        <v>86453</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2734,21 +2734,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4745</v>
+        <v>3739</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>808761</v>
+        <v>808709</v>
       </c>
       <c r="R21" t="n">
-        <v>7257304</v>
+        <v>7257177</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119788803</v>
+        <v>119788811</v>
       </c>
       <c r="B22" t="n">
-        <v>86336</v>
+        <v>97907</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3595</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Siljansspindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius dalecarlicus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>808624</v>
+        <v>808704</v>
       </c>
       <c r="R22" t="n">
-        <v>7257193</v>
+        <v>7257179</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2908,7 +2908,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2931,7 +2930,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119788814</v>
+        <v>119788815</v>
       </c>
       <c r="B23" t="n">
         <v>97907</v>
@@ -2971,10 +2970,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>808920</v>
+        <v>808879</v>
       </c>
       <c r="R23" t="n">
-        <v>7257293</v>
+        <v>7257278</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3037,10 +3036,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119788802</v>
+        <v>119788819</v>
       </c>
       <c r="B24" t="n">
-        <v>90067</v>
+        <v>97907</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3049,25 +3048,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>256703</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3077,10 +3076,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>808823</v>
+        <v>808646</v>
       </c>
       <c r="R24" t="n">
-        <v>7257295</v>
+        <v>7257196</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3143,10 +3142,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119788831</v>
+        <v>119788791</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
+        <v>87406</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3155,25 +3154,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4412</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3183,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>808801</v>
+        <v>808629</v>
       </c>
       <c r="R25" t="n">
-        <v>7257314</v>
+        <v>7257001</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3249,10 +3248,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119788812</v>
+        <v>119788800</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>91463</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3261,25 +3260,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3289,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>808704</v>
+        <v>808485</v>
       </c>
       <c r="R26" t="n">
-        <v>7257179</v>
+        <v>7256974</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3355,10 +3354,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119788800</v>
+        <v>119788803</v>
       </c>
       <c r="B27" t="n">
-        <v>91463</v>
+        <v>86336</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3367,25 +3366,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4745</v>
+        <v>3595</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Siljansspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cortinarius dalecarlicus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3395,10 +3394,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>808485</v>
+        <v>808624</v>
       </c>
       <c r="R27" t="n">
-        <v>7256974</v>
+        <v>7257193</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3439,6 +3438,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119788804</v>
+        <v>119788802</v>
       </c>
       <c r="B28" t="n">
-        <v>86453</v>
+        <v>90067</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3473,25 +3473,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3739</v>
+        <v>256703</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>808709</v>
+        <v>808823</v>
       </c>
       <c r="R28" t="n">
-        <v>7257177</v>
+        <v>7257295</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3567,7 +3567,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119788815</v>
+        <v>119788813</v>
       </c>
       <c r="B29" t="n">
         <v>97907</v>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>808879</v>
+        <v>808757</v>
       </c>
       <c r="R29" t="n">
-        <v>7257278</v>
+        <v>7257182</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119788813</v>
+        <v>119788801</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>91463</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3685,25 +3685,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>808757</v>
+        <v>808761</v>
       </c>
       <c r="R30" t="n">
-        <v>7257182</v>
+        <v>7257304</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3779,10 +3779,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119788807</v>
+        <v>119788814</v>
       </c>
       <c r="B31" t="n">
-        <v>94311</v>
+        <v>97907</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3791,25 +3791,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>808927</v>
+        <v>808920</v>
       </c>
       <c r="R31" t="n">
-        <v>7257295</v>
+        <v>7257293</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3885,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119788819</v>
+        <v>119788793</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>87406</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3897,25 +3897,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>808646</v>
+        <v>808662</v>
       </c>
       <c r="R32" t="n">
-        <v>7257196</v>
+        <v>7257218</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 14504-2020 artfynd.xlsx
+++ b/artfynd/A 14504-2020 artfynd.xlsx
@@ -1334,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119709354</v>
+        <v>119709382</v>
       </c>
       <c r="B8" t="n">
-        <v>96868</v>
+        <v>86381</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1346,25 +1346,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>248955</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>808673</v>
+        <v>808713</v>
       </c>
       <c r="R8" t="n">
-        <v>7257024</v>
+        <v>7257204</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,6 +1418,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1440,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119709382</v>
+        <v>119709354</v>
       </c>
       <c r="B9" t="n">
-        <v>86381</v>
+        <v>96868</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,25 +1453,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>248955</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1480,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>808713</v>
+        <v>808673</v>
       </c>
       <c r="R9" t="n">
-        <v>7257204</v>
+        <v>7257024</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1525,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119788819</v>
+        <v>119788791</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>87406</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3048,25 +3048,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>808646</v>
+        <v>808629</v>
       </c>
       <c r="R24" t="n">
-        <v>7257196</v>
+        <v>7257001</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,10 +3142,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119788791</v>
+        <v>119788819</v>
       </c>
       <c r="B25" t="n">
-        <v>87406</v>
+        <v>97907</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3154,25 +3154,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>808629</v>
+        <v>808646</v>
       </c>
       <c r="R25" t="n">
-        <v>7257001</v>
+        <v>7257196</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 14504-2020 artfynd.xlsx
+++ b/artfynd/A 14504-2020 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119709384</v>
+        <v>119709354</v>
       </c>
       <c r="B4" t="n">
-        <v>86336</v>
+        <v>96868</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3595</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Siljansspindling</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius dalecarlicus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>808638</v>
+        <v>808673</v>
       </c>
       <c r="R4" t="n">
-        <v>7257171</v>
+        <v>7257024</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119709360</v>
+        <v>119709342</v>
       </c>
       <c r="B5" t="n">
-        <v>91832</v>
+        <v>90334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,25 +1027,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>808653</v>
+        <v>808681</v>
       </c>
       <c r="R5" t="n">
-        <v>7257079</v>
+        <v>7257040</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119709383</v>
+        <v>119709337</v>
       </c>
       <c r="B6" t="n">
-        <v>86336</v>
+        <v>90509</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,25 +1133,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3595</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Siljansspindling</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius dalecarlicus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>808628</v>
+        <v>808664</v>
       </c>
       <c r="R6" t="n">
-        <v>7257172</v>
+        <v>7257170</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1228,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119709337</v>
+        <v>119709352</v>
       </c>
       <c r="B7" t="n">
-        <v>90509</v>
+        <v>90097</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,25 +1239,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>5747</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1268,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>808664</v>
+        <v>808716</v>
       </c>
       <c r="R7" t="n">
-        <v>7257170</v>
+        <v>7257151</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1441,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119709354</v>
+        <v>119709360</v>
       </c>
       <c r="B9" t="n">
-        <v>96868</v>
+        <v>91832</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,25 +1452,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1481,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>808673</v>
+        <v>808653</v>
       </c>
       <c r="R9" t="n">
-        <v>7257024</v>
+        <v>7257079</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119709342</v>
+        <v>119709384</v>
       </c>
       <c r="B10" t="n">
-        <v>90334</v>
+        <v>86336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,25 +1558,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3215</v>
+        <v>3595</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Siljansspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius dalecarlicus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1587,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>808681</v>
+        <v>808638</v>
       </c>
       <c r="R10" t="n">
-        <v>7257040</v>
+        <v>7257171</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119709352</v>
+        <v>119709383</v>
       </c>
       <c r="B11" t="n">
-        <v>90097</v>
+        <v>86336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,21 +1668,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5747</v>
+        <v>3595</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Siljansspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius dalecarlicus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>808716</v>
+        <v>808628</v>
       </c>
       <c r="R11" t="n">
-        <v>7257151</v>
+        <v>7257172</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,6 +1736,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119745816</v>
+        <v>119745790</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>87406</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,25 +1771,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>808568</v>
+        <v>808771</v>
       </c>
       <c r="R12" t="n">
-        <v>7256921</v>
+        <v>7257171</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1971,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119745814</v>
+        <v>119745805</v>
       </c>
       <c r="B14" t="n">
-        <v>91861</v>
+        <v>86336</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,41 +1983,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>3595</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Siljansspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Cortinarius dalecarlicus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Degerberget, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>808701</v>
+        <v>808703</v>
       </c>
       <c r="R14" t="n">
-        <v>7257191</v>
+        <v>7257179</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2081,10 +2078,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119745805</v>
+        <v>119745816</v>
       </c>
       <c r="B15" t="n">
-        <v>86336</v>
+        <v>91840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,25 +2090,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3595</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Siljansspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius dalecarlicus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2118,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>808703</v>
+        <v>808568</v>
       </c>
       <c r="R15" t="n">
-        <v>7257179</v>
+        <v>7256921</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,7 +2162,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2188,10 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119745817</v>
+        <v>119745814</v>
       </c>
       <c r="B16" t="n">
-        <v>95202</v>
+        <v>91861</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2204,34 +2200,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2869</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Degerberget, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>808679</v>
+        <v>808701</v>
       </c>
       <c r="R16" t="n">
-        <v>7257181</v>
+        <v>7257191</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2272,6 +2271,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2294,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119745790</v>
+        <v>119745817</v>
       </c>
       <c r="B17" t="n">
-        <v>87406</v>
+        <v>95202</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2306,25 +2306,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4412</v>
+        <v>2869</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>808771</v>
+        <v>808679</v>
       </c>
       <c r="R17" t="n">
-        <v>7257171</v>
+        <v>7257181</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,10 +2400,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119788807</v>
+        <v>119788812</v>
       </c>
       <c r="B18" t="n">
-        <v>94311</v>
+        <v>97907</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,25 +2412,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>808927</v>
+        <v>808704</v>
       </c>
       <c r="R18" t="n">
-        <v>7257295</v>
+        <v>7257179</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2506,10 +2506,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119788831</v>
+        <v>119788793</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>87406</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2518,25 +2518,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>4412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>808801</v>
+        <v>808662</v>
       </c>
       <c r="R19" t="n">
-        <v>7257314</v>
+        <v>7257218</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2612,10 +2612,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119788805</v>
+        <v>119788804</v>
       </c>
       <c r="B20" t="n">
-        <v>91832</v>
+        <v>86453</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2628,21 +2628,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>3739</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>808423</v>
+        <v>808709</v>
       </c>
       <c r="R20" t="n">
-        <v>7257034</v>
+        <v>7257177</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119788804</v>
+        <v>119788813</v>
       </c>
       <c r="B21" t="n">
-        <v>86453</v>
+        <v>97907</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2730,25 +2730,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3739</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>808709</v>
+        <v>808757</v>
       </c>
       <c r="R21" t="n">
-        <v>7257177</v>
+        <v>7257182</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119788811</v>
+        <v>119788805</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>91832</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>808704</v>
+        <v>808423</v>
       </c>
       <c r="R22" t="n">
-        <v>7257179</v>
+        <v>7257034</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2930,10 +2930,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119788815</v>
+        <v>119788801</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>91463</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,25 +2942,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>808879</v>
+        <v>808761</v>
       </c>
       <c r="R23" t="n">
-        <v>7257278</v>
+        <v>7257304</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119788791</v>
+        <v>119788831</v>
       </c>
       <c r="B24" t="n">
-        <v>87406</v>
+        <v>91840</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3048,25 +3048,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>808629</v>
+        <v>808801</v>
       </c>
       <c r="R24" t="n">
-        <v>7257001</v>
+        <v>7257314</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,10 +3142,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119788819</v>
+        <v>119788802</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>90067</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3154,25 +3154,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>256703</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>808646</v>
+        <v>808823</v>
       </c>
       <c r="R25" t="n">
-        <v>7257196</v>
+        <v>7257295</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3248,10 +3248,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119788800</v>
+        <v>119788807</v>
       </c>
       <c r="B26" t="n">
-        <v>91463</v>
+        <v>94311</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3260,25 +3260,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4745</v>
+        <v>2809</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>808485</v>
+        <v>808927</v>
       </c>
       <c r="R26" t="n">
-        <v>7256974</v>
+        <v>7257295</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119788803</v>
+        <v>119788800</v>
       </c>
       <c r="B27" t="n">
-        <v>86336</v>
+        <v>91463</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3366,25 +3366,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3595</v>
+        <v>4745</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Siljansspindling</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius dalecarlicus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>808624</v>
+        <v>808485</v>
       </c>
       <c r="R27" t="n">
-        <v>7257193</v>
+        <v>7256974</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3438,7 +3438,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3461,10 +3460,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119788802</v>
+        <v>119788814</v>
       </c>
       <c r="B28" t="n">
-        <v>90067</v>
+        <v>97907</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3473,25 +3472,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>256703</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3501,10 +3500,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>808823</v>
+        <v>808920</v>
       </c>
       <c r="R28" t="n">
-        <v>7257295</v>
+        <v>7257293</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3567,10 +3566,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119788813</v>
+        <v>119788803</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>86336</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3583,21 +3582,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>3595</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Siljansspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius dalecarlicus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3607,10 +3606,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>808757</v>
+        <v>808624</v>
       </c>
       <c r="R29" t="n">
-        <v>7257182</v>
+        <v>7257193</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3651,6 +3650,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119788801</v>
+        <v>119788819</v>
       </c>
       <c r="B30" t="n">
-        <v>91463</v>
+        <v>97907</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3685,25 +3685,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>808761</v>
+        <v>808646</v>
       </c>
       <c r="R30" t="n">
-        <v>7257304</v>
+        <v>7257196</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3779,10 +3779,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119788814</v>
+        <v>119788791</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>87406</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3791,25 +3791,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>808920</v>
+        <v>808629</v>
       </c>
       <c r="R31" t="n">
-        <v>7257293</v>
+        <v>7257001</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3885,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119788793</v>
+        <v>119788815</v>
       </c>
       <c r="B32" t="n">
-        <v>87406</v>
+        <v>97907</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3897,25 +3897,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>808662</v>
+        <v>808879</v>
       </c>
       <c r="R32" t="n">
-        <v>7257218</v>
+        <v>7257278</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 14504-2020 artfynd.xlsx
+++ b/artfynd/A 14504-2020 artfynd.xlsx
@@ -2184,10 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119745814</v>
+        <v>119745817</v>
       </c>
       <c r="B16" t="n">
-        <v>91861</v>
+        <v>95202</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2200,37 +2200,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>2869</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Degerberget, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>808701</v>
+        <v>808679</v>
       </c>
       <c r="R16" t="n">
-        <v>7257191</v>
+        <v>7257181</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,7 +2268,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2294,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119745817</v>
+        <v>119745814</v>
       </c>
       <c r="B17" t="n">
-        <v>95202</v>
+        <v>91861</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2310,34 +2306,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2869</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Degerberget, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>808679</v>
+        <v>808701</v>
       </c>
       <c r="R17" t="n">
-        <v>7257181</v>
+        <v>7257191</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2378,6 +2377,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -3248,10 +3248,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119788807</v>
+        <v>119788814</v>
       </c>
       <c r="B26" t="n">
-        <v>94311</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3260,25 +3260,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>808927</v>
+        <v>808920</v>
       </c>
       <c r="R26" t="n">
-        <v>7257295</v>
+        <v>7257293</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119788800</v>
+        <v>119788807</v>
       </c>
       <c r="B27" t="n">
-        <v>91463</v>
+        <v>94311</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3366,25 +3366,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4745</v>
+        <v>2809</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>808485</v>
+        <v>808927</v>
       </c>
       <c r="R27" t="n">
-        <v>7256974</v>
+        <v>7257295</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3460,10 +3460,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119788814</v>
+        <v>119788800</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>91463</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3472,25 +3472,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>808920</v>
+        <v>808485</v>
       </c>
       <c r="R28" t="n">
-        <v>7257293</v>
+        <v>7256974</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 14504-2020 artfynd.xlsx
+++ b/artfynd/A 14504-2020 artfynd.xlsx
@@ -2184,10 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119745817</v>
+        <v>119745814</v>
       </c>
       <c r="B16" t="n">
-        <v>95202</v>
+        <v>91861</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2200,34 +2200,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2869</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Degerberget, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>808679</v>
+        <v>808701</v>
       </c>
       <c r="R16" t="n">
-        <v>7257181</v>
+        <v>7257191</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,6 +2271,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2290,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119745814</v>
+        <v>119745817</v>
       </c>
       <c r="B17" t="n">
-        <v>91861</v>
+        <v>95202</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2306,37 +2310,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>2869</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Degerberget, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>808701</v>
+        <v>808679</v>
       </c>
       <c r="R17" t="n">
-        <v>7257191</v>
+        <v>7257181</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,7 +2378,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -3248,10 +3248,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119788814</v>
+        <v>119788807</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>94311</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3260,25 +3260,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>808920</v>
+        <v>808927</v>
       </c>
       <c r="R26" t="n">
-        <v>7257293</v>
+        <v>7257295</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119788807</v>
+        <v>119788800</v>
       </c>
       <c r="B27" t="n">
-        <v>94311</v>
+        <v>91463</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3366,25 +3366,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2809</v>
+        <v>4745</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>808927</v>
+        <v>808485</v>
       </c>
       <c r="R27" t="n">
-        <v>7257295</v>
+        <v>7256974</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3460,10 +3460,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119788800</v>
+        <v>119788814</v>
       </c>
       <c r="B28" t="n">
-        <v>91463</v>
+        <v>97907</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3472,25 +3472,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>808485</v>
+        <v>808920</v>
       </c>
       <c r="R28" t="n">
-        <v>7256974</v>
+        <v>7257293</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 14504-2020 artfynd.xlsx
+++ b/artfynd/A 14504-2020 artfynd.xlsx
@@ -3248,10 +3248,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119788807</v>
+        <v>119788814</v>
       </c>
       <c r="B26" t="n">
-        <v>94311</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3260,25 +3260,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>808927</v>
+        <v>808920</v>
       </c>
       <c r="R26" t="n">
-        <v>7257295</v>
+        <v>7257293</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119788800</v>
+        <v>119788807</v>
       </c>
       <c r="B27" t="n">
-        <v>91463</v>
+        <v>94311</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3366,25 +3366,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4745</v>
+        <v>2809</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>808485</v>
+        <v>808927</v>
       </c>
       <c r="R27" t="n">
-        <v>7256974</v>
+        <v>7257295</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3460,10 +3460,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119788814</v>
+        <v>119788800</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>91463</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3472,25 +3472,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>808920</v>
+        <v>808485</v>
       </c>
       <c r="R28" t="n">
-        <v>7257293</v>
+        <v>7256974</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 14504-2020 artfynd.xlsx
+++ b/artfynd/A 14504-2020 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119709354</v>
+        <v>119709352</v>
       </c>
       <c r="B4" t="n">
-        <v>96868</v>
+        <v>90114</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>5747</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>808673</v>
+        <v>808716</v>
       </c>
       <c r="R4" t="n">
-        <v>7257024</v>
+        <v>7257151</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,7 +1018,7 @@
         <v>119709342</v>
       </c>
       <c r="B5" t="n">
-        <v>90334</v>
+        <v>90351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>119709337</v>
       </c>
       <c r="B6" t="n">
-        <v>90509</v>
+        <v>90527</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119709352</v>
+        <v>119709354</v>
       </c>
       <c r="B7" t="n">
-        <v>90097</v>
+        <v>96891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1239,25 +1239,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5747</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>808716</v>
+        <v>808673</v>
       </c>
       <c r="R7" t="n">
-        <v>7257151</v>
+        <v>7257024</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119709382</v>
+        <v>119709383</v>
       </c>
       <c r="B8" t="n">
-        <v>86381</v>
+        <v>86353</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,21 +1349,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>248955</v>
+        <v>3595</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Siljansspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Cortinarius dalecarlicus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>808713</v>
+        <v>808628</v>
       </c>
       <c r="R8" t="n">
-        <v>7257204</v>
+        <v>7257172</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119709360</v>
+        <v>119709382</v>
       </c>
       <c r="B9" t="n">
-        <v>91832</v>
+        <v>86398</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,25 +1452,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>248955</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>808653</v>
+        <v>808713</v>
       </c>
       <c r="R9" t="n">
-        <v>7257079</v>
+        <v>7257204</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,6 +1524,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1546,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119709384</v>
+        <v>119709360</v>
       </c>
       <c r="B10" t="n">
-        <v>86336</v>
+        <v>91850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1558,25 +1559,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3595</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Siljansspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius dalecarlicus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1586,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>808638</v>
+        <v>808653</v>
       </c>
       <c r="R10" t="n">
-        <v>7257171</v>
+        <v>7257079</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119709383</v>
+        <v>119709384</v>
       </c>
       <c r="B11" t="n">
-        <v>86336</v>
+        <v>86353</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1692,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>808628</v>
+        <v>808638</v>
       </c>
       <c r="R11" t="n">
-        <v>7257172</v>
+        <v>7257171</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,7 +1737,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119745790</v>
+        <v>119745814</v>
       </c>
       <c r="B12" t="n">
-        <v>87406</v>
+        <v>91879</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,38 +1771,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4412</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Degerberget, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>808771</v>
+        <v>808701</v>
       </c>
       <c r="R12" t="n">
-        <v>7257171</v>
+        <v>7257191</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,6 +1846,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1865,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119745789</v>
+        <v>119745817</v>
       </c>
       <c r="B13" t="n">
-        <v>87406</v>
+        <v>95225</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,25 +1881,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4412</v>
+        <v>2869</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1905,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>808556</v>
+        <v>808679</v>
       </c>
       <c r="R13" t="n">
-        <v>7256898</v>
+        <v>7257181</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,7 +1978,7 @@
         <v>119745805</v>
       </c>
       <c r="B14" t="n">
-        <v>86336</v>
+        <v>86353</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2078,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119745816</v>
+        <v>119745789</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>87423</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,25 +2094,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>4412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2118,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>808568</v>
+        <v>808556</v>
       </c>
       <c r="R15" t="n">
-        <v>7256921</v>
+        <v>7256898</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119745814</v>
+        <v>119745790</v>
       </c>
       <c r="B16" t="n">
-        <v>91861</v>
+        <v>87423</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2196,41 +2200,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>4412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Degerberget, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>808701</v>
+        <v>808771</v>
       </c>
       <c r="R16" t="n">
-        <v>7257191</v>
+        <v>7257171</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,7 +2272,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2294,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119745817</v>
+        <v>119745816</v>
       </c>
       <c r="B17" t="n">
-        <v>95202</v>
+        <v>91858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2310,21 +2310,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2334,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>808679</v>
+        <v>808568</v>
       </c>
       <c r="R17" t="n">
-        <v>7257181</v>
+        <v>7256921</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,10 +2400,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119788812</v>
+        <v>119788800</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>91481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,25 +2412,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>808704</v>
+        <v>808485</v>
       </c>
       <c r="R18" t="n">
-        <v>7257179</v>
+        <v>7256974</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2506,10 +2506,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119788793</v>
+        <v>119788802</v>
       </c>
       <c r="B19" t="n">
-        <v>87406</v>
+        <v>90084</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2518,25 +2518,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4412</v>
+        <v>256703</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>808662</v>
+        <v>808823</v>
       </c>
       <c r="R19" t="n">
-        <v>7257218</v>
+        <v>7257295</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2612,10 +2612,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119788804</v>
+        <v>119788807</v>
       </c>
       <c r="B20" t="n">
-        <v>86453</v>
+        <v>94334</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2624,25 +2624,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3739</v>
+        <v>2809</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>808709</v>
+        <v>808927</v>
       </c>
       <c r="R20" t="n">
-        <v>7257177</v>
+        <v>7257295</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119788813</v>
+        <v>119788805</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>91850</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2730,25 +2730,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>808757</v>
+        <v>808423</v>
       </c>
       <c r="R21" t="n">
-        <v>7257182</v>
+        <v>7257034</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119788805</v>
+        <v>119788791</v>
       </c>
       <c r="B22" t="n">
-        <v>91832</v>
+        <v>87423</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>4412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>808423</v>
+        <v>808629</v>
       </c>
       <c r="R22" t="n">
-        <v>7257034</v>
+        <v>7257001</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2930,10 +2930,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119788801</v>
+        <v>119788814</v>
       </c>
       <c r="B23" t="n">
-        <v>91463</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,25 +2942,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>808761</v>
+        <v>808920</v>
       </c>
       <c r="R23" t="n">
-        <v>7257304</v>
+        <v>7257293</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119788831</v>
+        <v>119788803</v>
       </c>
       <c r="B24" t="n">
-        <v>91840</v>
+        <v>86353</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3048,25 +3048,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>3595</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Siljansspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius dalecarlicus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>808801</v>
+        <v>808624</v>
       </c>
       <c r="R24" t="n">
-        <v>7257314</v>
+        <v>7257193</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,6 +3120,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3142,10 +3143,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119788802</v>
+        <v>119788831</v>
       </c>
       <c r="B25" t="n">
-        <v>90067</v>
+        <v>91858</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3158,21 +3159,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3182,10 +3183,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>808823</v>
+        <v>808801</v>
       </c>
       <c r="R25" t="n">
-        <v>7257295</v>
+        <v>7257314</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3248,10 +3249,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119788814</v>
+        <v>119788793</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>87423</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3260,25 +3261,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3288,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>808920</v>
+        <v>808662</v>
       </c>
       <c r="R26" t="n">
-        <v>7257293</v>
+        <v>7257218</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3354,10 +3355,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119788807</v>
+        <v>119788819</v>
       </c>
       <c r="B27" t="n">
-        <v>94311</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3366,25 +3367,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3394,10 +3395,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>808927</v>
+        <v>808646</v>
       </c>
       <c r="R27" t="n">
-        <v>7257295</v>
+        <v>7257196</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3460,10 +3461,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119788800</v>
+        <v>119788801</v>
       </c>
       <c r="B28" t="n">
-        <v>91463</v>
+        <v>91481</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3500,10 +3501,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>808485</v>
+        <v>808761</v>
       </c>
       <c r="R28" t="n">
-        <v>7256974</v>
+        <v>7257304</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3566,10 +3567,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119788803</v>
+        <v>119788811</v>
       </c>
       <c r="B29" t="n">
-        <v>86336</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3582,21 +3583,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3595</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Siljansspindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius dalecarlicus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3606,10 +3607,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>808624</v>
+        <v>808704</v>
       </c>
       <c r="R29" t="n">
-        <v>7257193</v>
+        <v>7257179</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3650,7 +3651,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119788819</v>
+        <v>119788804</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>86470</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3685,25 +3685,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>3739</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>808646</v>
+        <v>808709</v>
       </c>
       <c r="R30" t="n">
-        <v>7257196</v>
+        <v>7257177</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3779,10 +3779,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119788791</v>
+        <v>119788813</v>
       </c>
       <c r="B31" t="n">
-        <v>87406</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3791,25 +3791,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>808629</v>
+        <v>808757</v>
       </c>
       <c r="R31" t="n">
-        <v>7257001</v>
+        <v>7257182</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3888,7 +3888,7 @@
         <v>119788815</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>119788827</v>
       </c>
       <c r="B33" t="n">
-        <v>91861</v>
+        <v>91879</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>119788809</v>
       </c>
       <c r="B34" t="n">
-        <v>91863</v>
+        <v>91881</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>119788828</v>
       </c>
       <c r="B35" t="n">
-        <v>91861</v>
+        <v>91879</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>

--- a/artfynd/A 14504-2020 artfynd.xlsx
+++ b/artfynd/A 14504-2020 artfynd.xlsx
@@ -2400,10 +2400,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119788800</v>
+        <v>119788814</v>
       </c>
       <c r="B18" t="n">
-        <v>91481</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,25 +2412,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>808485</v>
+        <v>808920</v>
       </c>
       <c r="R18" t="n">
-        <v>7256974</v>
+        <v>7257293</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2506,10 +2506,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119788802</v>
+        <v>119788803</v>
       </c>
       <c r="B19" t="n">
-        <v>90084</v>
+        <v>86353</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2518,25 +2518,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>256703</v>
+        <v>3595</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Siljansspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Cortinarius dalecarlicus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>808823</v>
+        <v>808624</v>
       </c>
       <c r="R19" t="n">
-        <v>7257295</v>
+        <v>7257193</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2590,6 +2590,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2612,10 +2613,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119788807</v>
+        <v>119788804</v>
       </c>
       <c r="B20" t="n">
-        <v>94334</v>
+        <v>86470</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2624,25 +2625,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2809</v>
+        <v>3739</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2652,10 +2653,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>808927</v>
+        <v>808709</v>
       </c>
       <c r="R20" t="n">
-        <v>7257295</v>
+        <v>7257177</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2824,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119788791</v>
+        <v>119788815</v>
       </c>
       <c r="B22" t="n">
-        <v>87423</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2836,25 +2837,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2864,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>808629</v>
+        <v>808879</v>
       </c>
       <c r="R22" t="n">
-        <v>7257001</v>
+        <v>7257278</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2930,10 +2931,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119788814</v>
+        <v>119788793</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>87423</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2942,25 +2943,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2970,10 +2971,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>808920</v>
+        <v>808662</v>
       </c>
       <c r="R23" t="n">
-        <v>7257293</v>
+        <v>7257218</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,10 +3037,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119788803</v>
+        <v>119788811</v>
       </c>
       <c r="B24" t="n">
-        <v>86353</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3052,21 +3053,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3595</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Siljansspindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius dalecarlicus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3076,10 +3077,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>808624</v>
+        <v>808704</v>
       </c>
       <c r="R24" t="n">
-        <v>7257193</v>
+        <v>7257179</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,7 +3121,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3143,10 +3143,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119788831</v>
+        <v>119788801</v>
       </c>
       <c r="B25" t="n">
-        <v>91858</v>
+        <v>91481</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3155,25 +3155,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>808801</v>
+        <v>808761</v>
       </c>
       <c r="R25" t="n">
-        <v>7257314</v>
+        <v>7257304</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3249,7 +3249,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119788793</v>
+        <v>119788791</v>
       </c>
       <c r="B26" t="n">
         <v>87423</v>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>808662</v>
+        <v>808629</v>
       </c>
       <c r="R26" t="n">
-        <v>7257218</v>
+        <v>7257001</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3355,10 +3355,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119788819</v>
+        <v>119788800</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>91481</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3367,25 +3367,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3395,10 +3395,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>808646</v>
+        <v>808485</v>
       </c>
       <c r="R27" t="n">
-        <v>7257196</v>
+        <v>7256974</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119788801</v>
+        <v>119788819</v>
       </c>
       <c r="B28" t="n">
-        <v>91481</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3473,25 +3473,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>808761</v>
+        <v>808646</v>
       </c>
       <c r="R28" t="n">
-        <v>7257304</v>
+        <v>7257196</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3567,10 +3567,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119788811</v>
+        <v>119788807</v>
       </c>
       <c r="B29" t="n">
-        <v>97930</v>
+        <v>94334</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3579,25 +3579,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>808704</v>
+        <v>808927</v>
       </c>
       <c r="R29" t="n">
-        <v>7257179</v>
+        <v>7257295</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119788804</v>
+        <v>119788802</v>
       </c>
       <c r="B30" t="n">
-        <v>86470</v>
+        <v>90084</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3685,25 +3685,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3739</v>
+        <v>256703</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>808709</v>
+        <v>808823</v>
       </c>
       <c r="R30" t="n">
-        <v>7257177</v>
+        <v>7257295</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3885,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119788815</v>
+        <v>119788831</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3897,25 +3897,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>808879</v>
+        <v>808801</v>
       </c>
       <c r="R32" t="n">
-        <v>7257278</v>
+        <v>7257314</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4101,10 +4101,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119788809</v>
+        <v>119788828</v>
       </c>
       <c r="B34" t="n">
-        <v>91881</v>
+        <v>91879</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4113,38 +4113,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Degerberget, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>808756</v>
+        <v>808673</v>
       </c>
       <c r="R34" t="n">
-        <v>7257294</v>
+        <v>7257226</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4185,6 +4188,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4207,10 +4211,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119788828</v>
+        <v>119788809</v>
       </c>
       <c r="B35" t="n">
-        <v>91879</v>
+        <v>91881</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4219,41 +4223,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5964</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Degerberget, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>808673</v>
+        <v>808756</v>
       </c>
       <c r="R35" t="n">
-        <v>7257226</v>
+        <v>7257294</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4294,7 +4295,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14504-2020 artfynd.xlsx
+++ b/artfynd/A 14504-2020 artfynd.xlsx
@@ -3461,10 +3461,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119788819</v>
+        <v>119788807</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>94334</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3473,25 +3473,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>808646</v>
+        <v>808927</v>
       </c>
       <c r="R28" t="n">
-        <v>7257196</v>
+        <v>7257295</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3567,10 +3567,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119788807</v>
+        <v>119788819</v>
       </c>
       <c r="B29" t="n">
-        <v>94334</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3579,25 +3579,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>808927</v>
+        <v>808646</v>
       </c>
       <c r="R29" t="n">
-        <v>7257295</v>
+        <v>7257196</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 14504-2020 artfynd.xlsx
+++ b/artfynd/A 14504-2020 artfynd.xlsx
@@ -4101,10 +4101,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119788828</v>
+        <v>119788809</v>
       </c>
       <c r="B34" t="n">
-        <v>91879</v>
+        <v>91881</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4113,41 +4113,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5964</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Degerberget, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>808673</v>
+        <v>808756</v>
       </c>
       <c r="R34" t="n">
-        <v>7257226</v>
+        <v>7257294</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4188,7 +4185,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4211,10 +4207,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119788809</v>
+        <v>119788828</v>
       </c>
       <c r="B35" t="n">
-        <v>91881</v>
+        <v>91879</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4223,38 +4219,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Degerberget, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>808756</v>
+        <v>808673</v>
       </c>
       <c r="R35" t="n">
-        <v>7257294</v>
+        <v>7257226</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4295,6 +4294,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14504-2020 artfynd.xlsx
+++ b/artfynd/A 14504-2020 artfynd.xlsx
@@ -4101,10 +4101,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119788809</v>
+        <v>119788828</v>
       </c>
       <c r="B34" t="n">
-        <v>91881</v>
+        <v>91879</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4113,38 +4113,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Degerberget, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>808756</v>
+        <v>808673</v>
       </c>
       <c r="R34" t="n">
-        <v>7257294</v>
+        <v>7257226</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4185,6 +4188,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4207,10 +4211,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119788828</v>
+        <v>119788809</v>
       </c>
       <c r="B35" t="n">
-        <v>91879</v>
+        <v>91881</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4219,41 +4223,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5964</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Degerberget, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>808673</v>
+        <v>808756</v>
       </c>
       <c r="R35" t="n">
-        <v>7257226</v>
+        <v>7257294</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4294,7 +4295,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
